--- a/data/trans_bre/P16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,26</t>
+          <t>-3,89; 1,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,7</t>
+          <t>-5,03; 0,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,21</t>
+          <t>-3,32; 2,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,77</t>
+          <t>-2,65; 3,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 11,47</t>
+          <t>-28,62; 13,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 6,54</t>
+          <t>-34,4; 6,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 28,88</t>
+          <t>-23,15; 24,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,85; 28,49</t>
+          <t>-15,14; 29,57</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,4</t>
+          <t>-1,64; 0,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; -0,18</t>
+          <t>-1,92; -0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,66</t>
+          <t>-3,02; -0,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,13</t>
+          <t>-2,49; -0,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 24,1</t>
+          <t>-56,14; 20,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,76; -8,2</t>
+          <t>-67,6; -2,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,49; -18,11</t>
+          <t>-60,98; -18,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,39; -9,94</t>
+          <t>-59,64; -8,99</t>
         </is>
       </c>
     </row>
@@ -860,17 +860,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,37</t>
+          <t>-2,12; 1,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,0</t>
+          <t>-3,11; -0,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,63</t>
+          <t>-2,76; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,08; 128,87</t>
+          <t>-73,23; 120,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,9</t>
+          <t>-100,0; 40,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,94; 85,61</t>
+          <t>-63,77; 78,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-73,18; -15,13</t>
+          <t>-72,01; -15,43</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,29; 0,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,58</t>
+          <t>-1,51; 0,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,46</t>
+          <t>-1,78; 0,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,84</t>
+          <t>-1,7; 0,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 20,74</t>
+          <t>-21,61; 18,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 12,76</t>
+          <t>-25,71; 12,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 8,42</t>
+          <t>-27,4; 11,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 16,85</t>
+          <t>-28,39; 18,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A10-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A10-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,46</t>
+          <t>-3,98; 1,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,64</t>
+          <t>-5,02; 0,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,79</t>
+          <t>-3,25; 3,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 3,85</t>
+          <t>-2,28; 4,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 13,6</t>
+          <t>-28,39; 10,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,4; 6,0</t>
+          <t>-35,38; 5,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 24,71</t>
+          <t>-22,86; 33,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 29,57</t>
+          <t>-13,55; 34,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,89%</t>
+          <t>-38,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,36</t>
+          <t>-1,6; 0,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,1</t>
+          <t>-1,95; -0,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,64</t>
+          <t>-2,93; -0,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,49; -0,12</t>
+          <t>-2,44; -0,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,14; 20,8</t>
+          <t>-56,14; 20,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -2,03</t>
+          <t>-68,14; -4,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,98; -18,41</t>
+          <t>-59,79; -13,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,64; -8,99</t>
+          <t>-52,75; -13,69</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,93</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,02%</t>
+          <t>-53,57%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,35</t>
+          <t>-2,22; 1,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,11</t>
+          <t>-2,98; -0,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,65</t>
+          <t>-2,75; 1,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; -0,51</t>
+          <t>-3,79; -0,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 120,53</t>
+          <t>-74,84; 126,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,57</t>
+          <t>-100,0; 36,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,77; 78,6</t>
+          <t>-64,03; 82,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,01; -15,43</t>
+          <t>-71,53; -20,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,49</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-8,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,91</t>
+          <t>-1,29; 0,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,64</t>
+          <t>-1,61; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,61</t>
+          <t>-1,74; 0,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,88</t>
+          <t>-1,42; 0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 18,91</t>
+          <t>-20,98; 18,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 12,93</t>
+          <t>-27,49; 12,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,4; 11,67</t>
+          <t>-27,18; 10,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 18,3</t>
+          <t>-22,54; 7,52</t>
         </is>
       </c>
     </row>
